--- a/dispositivi_mancanti.xlsx
+++ b/dispositivi_mancanti.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Dispositivi Mancanti" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Modelli comuni" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dispositivi Mancanti'!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dispositivi Mancanti'!$A$1:$F$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,10 +38,11 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="009E9E9E"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,12 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="00EBF5FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF5FB"/>
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,16 +109,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,10 +483,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
@@ -525,12 +529,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Barberino di Mugello</t>
+          <t>Camaiore</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Corsini</t>
+          <t>Borsalino</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -538,19 +542,27 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Barga</t>
+          <t>Capannori</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Artè</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -558,19 +570,27 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Camaiore</t>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Borsalino</t>
+          <t>Nuovo Cinema Caporali</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -578,32 +598,48 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Capannori</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Castiglione del Lago</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Artè</t>
+          <t>Nuovo Cinema Caporali</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Castiglione del Lago</t>
         </is>
@@ -615,422 +651,550 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Castiglione del Lago</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Cortona</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nuovo Cinema Caporali</t>
+          <t>Teatro Signorelli</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Astra</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Castello</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Castello</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Castiglione del Lago</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Nuovo Cinema Caporali</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Marconi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Marconi</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Marconi</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Sala 3</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Cortona</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Teatro Signorelli</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Astra</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Odeon</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Cinema Castello</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Everest</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Cinema Marconi</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Fiamma</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Cinema Marconi</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Fiamma</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Cinema Marconi</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Sala 3</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cinema Odeon</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Sala 4</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Everest</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Il Portico</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Fiamma</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Il Portico</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Fiamma</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Principe</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Principe</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Sala 3</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Sala 4</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Il Portico</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Il Portico</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Principe</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Principe</t>
+          <t>Sala Esse</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Firenze</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Firenzuola</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Sala Esse</t>
+          <t>Don Otello Puccetti</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1038,19 +1202,27 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Firenzuola</t>
+          <t>Fornaci di Barga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Don Otello Puccetti</t>
+          <t>Puccini</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1058,19 +1230,27 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Fornaci di Barga</t>
+          <t>Forte dei Marmi</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Puccini</t>
+          <t>Nuovo Lido</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1078,12 +1258,20 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Forte dei Marmi</t>
         </is>
@@ -1095,12 +1283,20 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1118,9 +1314,9 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1138,9 +1334,17 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1158,12 +1362,12 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Livorno</t>
         </is>
@@ -1178,12 +1382,20 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Livorno</t>
         </is>
@@ -1198,9 +1410,17 @@
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1218,9 +1438,17 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1238,12 +1466,20 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Montecatini Terme</t>
         </is>
@@ -1258,9 +1494,17 @@
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1278,12 +1522,20 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1298,12 +1550,20 @@
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1318,12 +1578,20 @@
           <t>Sala 3</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1338,12 +1606,20 @@
           <t>Sala 4</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1358,12 +1634,20 @@
           <t>Sala 5</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1378,12 +1662,20 @@
           <t>Sala 6</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1398,12 +1690,20 @@
           <t>Sala 7</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Montevarchi</t>
         </is>
@@ -1418,9 +1718,17 @@
           <t>Sala 8</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1438,9 +1746,17 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr"/>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1458,9 +1774,17 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1478,12 +1802,20 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
@@ -1498,12 +1830,20 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Pisa</t>
         </is>
@@ -1518,9 +1858,17 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1538,79 +1886,111 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Pontassieve</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Accademia</t>
+          <t>Lux</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Pontedera</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Agorà</t>
+          <t>Lux</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Portoferraio</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Nello Santi</t>
+          <t>Lux</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+          <t>Sala 4</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>Pontassieve</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Cinema Eden</t>
+          <t>Accademia</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -1618,19 +1998,27 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Prato</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Terminale</t>
+          <t>Agorà</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -1638,19 +2026,27 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Reggello</t>
+          <t>Portoferraio</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Cinema Excelsior</t>
+          <t>Nello Santi</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -1658,139 +2054,195 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>Prato</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Eden</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Prato</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Eden</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Prato</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Eden</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Prato</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Terminale</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Reggello</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Excelsior</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>San Vincenzo</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Cinema Verdi</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Santa Croce sull'Arno</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Lami</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Santa Croce sull'Arno</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Lami</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Santa Croce sull'Arno</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Lami</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Sala 3</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Santa Croce sull'Arno</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Lami</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Sala 4</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Santa Croce sull'Arno</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Lami</t>
-        </is>
-      </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Sala 5</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Scandicci</t>
+          <t>Santa Croce sull'Arno</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Cabiria</t>
+          <t>Lami</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -1798,210 +2250,356 @@
           <t>Sala 1</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr"/>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Seravezza</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Santa Croce sull'Arno</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Scuderie Granducali</t>
+          <t>Lami</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Siena</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Santa Croce sull'Arno</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Metropolitan</t>
+          <t>Lami</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Siena</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Santa Croce sull'Arno</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Pendola</t>
+          <t>Lami</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+          <t>Sala 4</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Viareggio</t>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Santa Croce sull'Arno</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Cinema Centrale</t>
+          <t>Lami</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>Sala 5</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>Scandicci</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Cabiria</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Scandicci</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Cabiria</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Siena</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Metropolitan</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Siena</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Pendola</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Viareggio</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Cinema Centrale</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>Villafranca in Lunigiana</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Città di Villafranca</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Volterra</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Centrale</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr"/>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Volterra</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Centrale</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F71"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>MODELLI COMUNI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Christie IMB / Dolby IMS3000 / ShowVault / Qube XP-D / GDC SX-3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Barco DP2K-8S / Barco DP2K-10S / Barco DP2K-12C / Barco DP2K-15C / Barco DP2K-19B</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Barco SP2K-10 / Barco SP2K-15 / Christie CP2210 / NEC NC1200C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Processore Audio</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dolby CP750 / Dolby CP850 / Dolby CP950 / Dolby CP500 / QSC DCP-300</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:F77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dispositivi_mancanti.xlsx
+++ b/dispositivi_mancanti.xlsx
@@ -446,11 +446,11 @@
   <dimension ref="A1:F461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -514,7 +514,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.57.91.1:161</t>
+          <t>10.57.91.1</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.57.91.2:161</t>
+          <t>10.57.91.2</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.57.91.12:161</t>
+          <t>10.57.91.12</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.57.91.12:161</t>
+          <t>10.57.91.12</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.57.91.14:161</t>
+          <t>10.57.91.14</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.57.91.22:161</t>
+          <t>10.57.91.22</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10.57.91.22:161</t>
+          <t>10.57.91.22</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.57.91.24:161</t>
+          <t>10.57.91.24</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.57.91.32:161</t>
+          <t>10.57.91.32</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.57.91.32:161</t>
+          <t>10.57.91.32</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.57.91.34:161</t>
+          <t>10.57.91.34</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10.57.91.42:161</t>
+          <t>10.57.91.42</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10.57.91.42:161</t>
+          <t>10.57.91.42</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10.57.91.44:161</t>
+          <t>10.57.91.44</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.56.70.1:161</t>
+          <t>10.56.70.1</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.56.70.10:161</t>
+          <t>10.56.70.10</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10.56.70.12:161</t>
+          <t>10.56.70.12</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.56.70.14:161</t>
+          <t>10.56.70.14</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10.56.70.20:161</t>
+          <t>10.56.70.20</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.56.70.22:161</t>
+          <t>10.56.70.22</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.56.70.24:161</t>
+          <t>10.56.70.24</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.56.70.30:161</t>
+          <t>10.56.70.30</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10.56.70.32:161</t>
+          <t>10.56.70.32</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10.56.70.34:161</t>
+          <t>10.56.70.34</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10.56.70.40:161</t>
+          <t>10.56.70.40</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.56.70.42:161</t>
+          <t>10.56.70.42</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.56.70.44:161</t>
+          <t>10.56.70.44</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10.56.70.50:161</t>
+          <t>10.56.70.50</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10.56.70.52:161</t>
+          <t>10.56.70.52</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10.56.70.54:161</t>
+          <t>10.56.70.54</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.56.70.60:161</t>
+          <t>10.56.70.60</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10.56.70.62:161</t>
+          <t>10.56.70.62</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10.56.70.64:161</t>
+          <t>10.56.70.64</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10.57.97.1:161</t>
+          <t>10.57.97.1</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.57.97.2:161</t>
+          <t>10.57.97.2</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.57.97.10:161</t>
+          <t>10.57.97.10</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.57.97.12:161</t>
+          <t>10.57.97.12</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.57.97.14:161</t>
+          <t>10.57.97.14</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10.57.97.20:161</t>
+          <t>10.57.97.20</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.57.97.22:161</t>
+          <t>10.57.97.22</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10.57.97.24:161</t>
+          <t>10.57.97.24</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.57.97.32:161</t>
+          <t>10.57.97.32</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.57.97.32:161</t>
+          <t>10.57.97.32</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.57.97.34:161</t>
+          <t>10.57.97.34</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.57.97.42:161</t>
+          <t>10.57.97.42</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10.57.97.42:161</t>
+          <t>10.57.97.42</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10.57.97.44:161</t>
+          <t>10.57.97.44</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10.58.70.1:161</t>
+          <t>10.58.70.1</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10.58.70.10:161</t>
+          <t>10.58.70.10</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.58.70.12:161</t>
+          <t>10.58.70.12</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10.58.70.14:161</t>
+          <t>10.58.70.14</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10.58.70.20:161</t>
+          <t>10.58.70.20</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10.58.70.22:161</t>
+          <t>10.58.70.22</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10.58.70.24:161</t>
+          <t>10.58.70.24</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10.58.70.30:161</t>
+          <t>10.58.70.30</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10.58.70.32:161</t>
+          <t>10.58.70.32</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10.58.70.34:161</t>
+          <t>10.58.70.34</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10.55.76.1:161</t>
+          <t>10.55.76.1</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10.55.76.2:161</t>
+          <t>10.55.76.2</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>10.55.76.10:161</t>
+          <t>10.55.76.10</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10.55.76.12:161</t>
+          <t>10.55.76.12</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10.55.76.14:161</t>
+          <t>10.55.76.14</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10.55.76.209:161</t>
+          <t>10.55.76.209</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.55.76.20:161</t>
+          <t>10.55.76.20</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10.55.76.22:161</t>
+          <t>10.55.76.22</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10.55.76.24:161</t>
+          <t>10.55.76.24</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10.55.76.30:161</t>
+          <t>10.55.76.30</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10.55.76.32:161</t>
+          <t>10.55.76.32</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10.55.76.34:161</t>
+          <t>10.55.76.34</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>10.55.76.40:161</t>
+          <t>10.55.76.40</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10.55.76.42:161</t>
+          <t>10.55.76.42</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10.55.76.44:161</t>
+          <t>10.55.76.44</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>10.55.76.50:161</t>
+          <t>10.55.76.50</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10.55.76.52:161</t>
+          <t>10.55.76.52</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10.55.76.54:161</t>
+          <t>10.55.76.54</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10.58.76.1:161</t>
+          <t>10.58.76.1</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10.58.76.10:161</t>
+          <t>10.58.76.10</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10.58.76.12:161</t>
+          <t>10.58.76.12</t>
         </is>
       </c>
     </row>
@@ -3010,14 +3010,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10.58.76.14:161</t>
+          <t>10.58.76.14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Giunti Odeon</t>
+          <t>Cinema Odeon</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3042,14 +3042,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10.58.79.1:161</t>
+          <t>10.58.79.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Giunti Odeon</t>
+          <t>Cinema Odeon</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10.58.79.12:161</t>
+          <t>10.58.79.12</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Giunti Odeon</t>
+          <t>Cinema Odeon</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>10.58.79.12:161</t>
+          <t>10.58.79.12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Giunti Odeon</t>
+          <t>Cinema Odeon</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>10.58.79.14:161</t>
+          <t>10.58.79.14</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>10.58.77.1:161</t>
+          <t>10.58.77.1</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10.58.77.10:161</t>
+          <t>10.58.77.10</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>10.58.77.12:161</t>
+          <t>10.58.77.12</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>10.58.77.14:161</t>
+          <t>10.58.77.14</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10.58.75.1:161</t>
+          <t>10.58.75.1</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10.58.75.10:161</t>
+          <t>10.58.75.10</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>10.58.75.12:161</t>
+          <t>10.58.75.12</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>10.58.75.14:161</t>
+          <t>10.58.75.14</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>10.58.75.20:161</t>
+          <t>10.58.75.20</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>10.58.75.22:161</t>
+          <t>10.58.75.22</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>10.58.75.24:161</t>
+          <t>10.58.75.24</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>10.58.75.30:161</t>
+          <t>10.58.75.30</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>10.58.75.32:161</t>
+          <t>10.58.75.32</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>10.58.75.34:161</t>
+          <t>10.58.75.34</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>10.58.78.1:161</t>
+          <t>10.58.78.1</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>10.58.78.10:161</t>
+          <t>10.58.78.10</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>10.58.78.12:161</t>
+          <t>10.58.78.12</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>10.58.78.14:161</t>
+          <t>10.58.78.14</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>10.58.78.22:161</t>
+          <t>10.58.78.22</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10.58.78.22:161</t>
+          <t>10.58.78.22</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>10.58.78.24:161</t>
+          <t>10.58.78.24</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>10.58.71.1:161</t>
+          <t>10.58.71.1</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>10.58.71.10:161</t>
+          <t>10.58.71.10</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>10.58.71.12:161</t>
+          <t>10.58.71.12</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>10.58.71.14:161</t>
+          <t>10.58.71.14</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>10.58.71.20:161</t>
+          <t>10.58.71.20</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>10.58.71.22:161</t>
+          <t>10.58.71.22</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>10.58.71.24:161</t>
+          <t>10.58.71.24</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>10.58.71.30:161</t>
+          <t>10.58.71.30</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>10.58.71.32:161</t>
+          <t>10.58.71.32</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>10.58.71.34:161</t>
+          <t>10.58.71.34</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>10.58.71.40:161</t>
+          <t>10.58.71.40</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>10.58.71.42:161</t>
+          <t>10.58.71.42</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>10.58.71.44:161</t>
+          <t>10.58.71.44</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>10.58.71.50:161</t>
+          <t>10.58.71.50</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>10.58.71.52:161</t>
+          <t>10.58.71.52</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>10.58.71.54:161</t>
+          <t>10.58.71.54</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>10.58.71.60:161</t>
+          <t>10.58.71.60</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>10.58.71.62:161</t>
+          <t>10.58.71.62</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>10.58.71.64:161</t>
+          <t>10.58.71.64</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>10.58.71.70:161</t>
+          <t>10.58.71.70</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>10.58.71.72:161</t>
+          <t>10.58.71.72</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>10.58.71.74:161</t>
+          <t>10.58.71.74</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>10.58.84.1:161</t>
+          <t>10.58.84.1</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>10.58.84.10:161</t>
+          <t>10.58.84.10</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>10.58.84.12:161</t>
+          <t>10.58.84.12</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>10.58.84.14:161</t>
+          <t>10.58.84.14</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>10.58.84.20:161</t>
+          <t>10.58.84.20</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>10.58.84.22:161</t>
+          <t>10.58.84.22</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>10.58.84.24:161</t>
+          <t>10.58.84.24</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>10.58.82.1:161</t>
+          <t>10.58.82.1</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>10.58.82.10:161</t>
+          <t>10.58.82.10</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>10.58.82.12:161</t>
+          <t>10.58.82.12</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>10.58.82.14:161</t>
+          <t>10.58.82.14</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>10.58.81.1:161</t>
+          <t>10.58.81.1</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>10.58.81.12:161</t>
+          <t>10.58.81.12</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>10.58.81.12:161</t>
+          <t>10.58.81.12</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>10.58.81.14:161</t>
+          <t>10.58.81.14</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>10.56.89.1:161</t>
+          <t>10.56.89.1</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>10.56.89.10:161</t>
+          <t>10.56.89.10</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>10.56.89.12:161</t>
+          <t>10.56.89.12</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>10.56.89.14:161</t>
+          <t>10.56.89.14</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>10.58.83.1:161</t>
+          <t>10.58.83.1</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>10.58.83.12:161</t>
+          <t>10.58.83.12</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>10.58.83.12:161</t>
+          <t>10.58.83.12</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>10.58.83.14:161</t>
+          <t>10.58.83.14</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>10.58.83.22:161</t>
+          <t>10.58.83.22</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>10.58.83.22:161</t>
+          <t>10.58.83.22</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>10.58.83.24:161</t>
+          <t>10.58.83.24</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>192.168.1.134:161</t>
+          <t>192.168.1.134</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>192.168.1.134:161</t>
+          <t>192.168.1.134</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>192.168.1.136:161</t>
+          <t>192.168.1.136</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>192.168.1.30:161</t>
+          <t>192.168.1.30</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.32:161</t>
+          <t>192.168.1.32</t>
         </is>
       </c>
     </row>
@@ -7490,14 +7490,14 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>192.168.1.34:161</t>
+          <t>192.168.1.34</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Cinema Odeon</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7522,14 +7522,14 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Cinema Odeon</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7554,14 +7554,14 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Cinema Odeon</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7581,19 +7581,19 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Barco DP2K-19B</t>
+          <t>Barco DP2K-10S</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Cinema Odeon</t>
+          <t>Everest</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7618,14 +7618,14 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Fiamma</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7650,14 +7650,14 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Fiamma</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7677,51 +7677,51 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Barco ICMP</t>
+          <t>Qube XP-D</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Everest</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Fiamma</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Barco DP2K-10S</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>192.168.1.12:161</t>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Everest</t>
+          <t>Fiamma</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -7768,88 +7768,88 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Rete</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>MikroTik</t>
+          <t>Qube XP-D</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>Fiamma</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Qube XP-D</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>192.168.1.10:161</t>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+      <c r="A231" t="inlineStr">
         <is>
           <t>Fiamma</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.12:161</t>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Dolby CP750</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Fiamma</t>
+          <t>Flora</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7864,56 +7864,56 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Rete</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Dolby CP750</t>
+          <t>MikroTik</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Fiamma</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Qube XP-D</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>192.168.1.20:161</t>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Fiamma</t>
+          <t>Flora</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -7928,465 +7928,465 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>Processore Audio</t>
+        </is>
+      </c>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>192.168.1.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Proiettore</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.22:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Fiamma</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
         <is>
           <t>Sala 2</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Dolby CP750</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>192.168.1.24:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>Processore Audio</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>192.168.1.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
         <is>
           <t>Flora</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B239" s="3" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>Sala 3</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>Processore Audio</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>192.168.1.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Sala 4</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Sala 4</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Flora</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>Sala 4</t>
+        </is>
+      </c>
+      <c r="E244" s="4" t="inlineStr">
+        <is>
+          <t>Processore Audio</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>192.168.1.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Il Portico</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Firenze</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
         <is>
           <t>Rete</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>MikroTik</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>192.168.1.1:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>192.168.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Il Portico</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.10:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Barco ICMP</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>192.168.1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Il Portico</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.12:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Barco DP2K-10S</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Il Portico</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C239" s="4" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D239" s="4" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E239" s="4" t="inlineStr">
-        <is>
-          <t>Processore Audio</t>
-        </is>
-      </c>
-      <c r="F239" s="4" t="inlineStr">
-        <is>
-          <t>192.168.1.14:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.20:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F241" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.22:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>Processore Audio</t>
-        </is>
-      </c>
-      <c r="F242" s="4" t="inlineStr">
-        <is>
-          <t>192.168.1.24:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C243" s="3" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>Sala 3</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.30:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>Sala 3</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.32:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>Sala 3</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>Processore Audio</t>
-        </is>
-      </c>
-      <c r="F245" s="4" t="inlineStr">
-        <is>
-          <t>192.168.1.34:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>Sala 4</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.40:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>Sala 4</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F247" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.42:161</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>Flora</t>
-        </is>
-      </c>
-      <c r="B248" s="4" t="inlineStr">
-        <is>
-          <t>Firenze</t>
-        </is>
-      </c>
-      <c r="C248" s="4" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>Sala 4</t>
-        </is>
-      </c>
-      <c r="E248" s="4" t="inlineStr">
-        <is>
-          <t>Processore Audio</t>
-        </is>
-      </c>
-      <c r="F248" s="4" t="inlineStr">
-        <is>
-          <t>192.168.1.44:161</t>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Dolby CP650</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -8408,17 +8408,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Rete</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>MikroTik</t>
+          <t>Doremi ShowVault</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -8440,17 +8440,17 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Barco ICMP</t>
+          <t>Barco DP2K-20C</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -8472,24 +8472,24 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Barco DP2K-10S</t>
+          <t>Dolby CP65</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Il Portico</t>
+          <t>Principe</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8504,24 +8504,24 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Rete</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Dolby CP650</t>
+          <t>MikroTik</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Il Portico</t>
+          <t>Principe</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8536,56 +8536,56 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Sala 2</t>
+          <t>Sala 1</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Doremi ShowVault</t>
+          <t>Qube XP-D</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Il Portico</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Principe</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>Barco DP2K-20C</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>192.168.1.22:161</t>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Il Portico</t>
+          <t>Principe</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Sala 2</t>
+          <t>Sala 1</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Dolby CP65</t>
+          <t>Dolby CP750</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -8632,88 +8632,88 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Rete</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>MikroTik</t>
+          <t>Qube XP-D</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>Principe</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Qube XP-D</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>192.168.1.10:161</t>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+      <c r="A258" t="inlineStr">
         <is>
           <t>Principe</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.12:161</t>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Sala 2</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Dolby CP750</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Principe</t>
+          <t>Sala Esse</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8728,24 +8728,24 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Rete</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Dolby CP750</t>
+          <t>MikroTik</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Principe</t>
+          <t>Sala Esse</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8760,56 +8760,56 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Sala 2</t>
+          <t>Sala 1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Qube XP-D</t>
+          <t>Doremi ShowVault</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>Principe</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Sala Esse</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
         <is>
           <t>Firenze</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F261" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.22:161</t>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Barco DP2K-20C</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Principe</t>
+          <t>Sala Esse</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8824,29 +8824,29 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Sala 2</t>
+          <t>Sala 1</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Dolby CP750</t>
+          <t>Dolby CP650</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Sala Esse</t>
+          <t>Don Otello Puccetti</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Firenzuola</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8866,19 +8866,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Sala Esse</t>
+          <t>Don Otello Puccetti</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Firenzuola</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8898,19 +8898,19 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Sala Esse</t>
+          <t>Don Otello Puccetti</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Firenzuola</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8930,19 +8930,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Sala Esse</t>
+          <t>Don Otello Puccetti</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Firenzuola</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8957,24 +8957,24 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Dolby CP650</t>
+          <t>Dolby CP950</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Don Otello Puccetti</t>
+          <t>Puccini</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Firenzuola</t>
+          <t>Fornaci di Barga</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8994,19 +8994,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Don Otello Puccetti</t>
+          <t>Puccini</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Firenzuola</t>
+          <t>Fornaci di Barga</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9026,19 +9026,19 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Don Otello Puccetti</t>
+          <t>Puccini</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Firenzuola</t>
+          <t>Fornaci di Barga</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9053,24 +9053,24 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Barco DP2K-20C</t>
+          <t>Cinemeccanica DPC-80</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Don Otello Puccetti</t>
+          <t>Puccini</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Firenzuola</t>
+          <t>Fornaci di Barga</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -9085,24 +9085,24 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Dolby CP950</t>
+          <t>Dolby CP650</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Puccini</t>
+          <t>Nuovo Lido</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Fornaci di Barga</t>
+          <t>Forte dei Marmi</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -9122,19 +9122,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Puccini</t>
+          <t>Nuovo Lido</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Fornaci di Barga</t>
+          <t>Forte dei Marmi</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Puccini</t>
+          <t>Nuovo Lido</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Fornaci di Barga</t>
+          <t>Forte dei Marmi</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -9181,24 +9181,24 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Cinemeccanica DPC-80</t>
+          <t>Barco DP2K-20C</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Puccini</t>
+          <t>Nuovo Lido</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Fornaci di Barga</t>
+          <t>Forte dei Marmi</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Rete</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>MikroTik</t>
+          <t>Doremi ShowVault</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -9272,17 +9272,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Doremi ShowVault</t>
+          <t>Barco DP2K-20C</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -9304,29 +9304,29 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Sala 2</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Barco DP2K-20C</t>
+          <t>Dolby CP650</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Nuovo Lido</t>
+          <t>Teatro Pacini</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Forte dei Marmi</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -9336,93 +9336,93 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Sala 1</t>
+          <t>Rete</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Dolby CP650</t>
+          <t>MikroTik</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Nuovo Lido</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Forte dei Marmi</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Doremi ShowVault</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>192.168.1.20:161</t>
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>Teatro Pacini</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>Fucecchio</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Nuovo Lido</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Forte dei Marmi</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Sala 2</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Barco DP2K-20C</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>192.168.1.22:161</t>
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Teatro Pacini</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Fucecchio</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Proiettore</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Nuovo Lido</t>
+          <t>Teatro Pacini</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Forte dei Marmi</t>
+          <t>Fucecchio</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -9432,29 +9432,29 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Sala 2</t>
+          <t>Sala 1</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Dolby CP650</t>
+          <t>Dolby CP750</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Teatro Pacini</t>
+          <t>Florentia</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
+          <t>Larderello</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -9474,83 +9474,83 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="3" t="inlineStr">
-        <is>
-          <t>Teatro Pacini</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>Fucecchio</t>
-        </is>
-      </c>
-      <c r="C283" s="3" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D283" s="3" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E283" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.10:161</t>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Florentia</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Larderello</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Doremi ShowVault</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>Teatro Pacini</t>
-        </is>
-      </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>Fucecchio</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
-        <is>
-          <t>Sala 1</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>Proiettore</t>
-        </is>
-      </c>
-      <c r="F284" s="2" t="inlineStr">
-        <is>
-          <t>192.168.1.12:161</t>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Florentia</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Larderello</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Sala 1</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Barco DP2K-20C</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Teatro Pacini</t>
+          <t>Florentia</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Fucecchio</t>
+          <t>Larderello</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9565,24 +9565,24 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Dolby CP750</t>
+          <t>Dolby CP65</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Florentia</t>
+          <t>Teatro delle Arti</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Larderello</t>
+          <t>Lastra a Signa</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9602,19 +9602,19 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Florentia</t>
+          <t>Teatro delle Arti</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Larderello</t>
+          <t>Lastra a Signa</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9634,19 +9634,19 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Florentia</t>
+          <t>Teatro delle Arti</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Larderello</t>
+          <t>Lastra a Signa</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9661,24 +9661,24 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Barco DP2K-20C</t>
+          <t>Barco DP2K-10S</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Florentia</t>
+          <t>Teatro delle Arti</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Larderello</t>
+          <t>Lastra a Signa</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Dolby CP65</t>
+          <t>Dolby CP750</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>192.168.1.134:161</t>
+          <t>192.168.1.134</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>192.168.1.136:161</t>
+          <t>192.168.1.136</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>192.168.1.30:161</t>
+          <t>192.168.1.30</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.32:161</t>
+          <t>192.168.1.32</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.34:161</t>
+          <t>192.168.1.34</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>192.168.1.40:161</t>
+          <t>192.168.1.40</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F323" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.42:161</t>
+          <t>192.168.1.42</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.44:161</t>
+          <t>192.168.1.44</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>192.168.1.50:161</t>
+          <t>192.168.1.50</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.52:161</t>
+          <t>192.168.1.52</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.54:161</t>
+          <t>192.168.1.54</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>192.168.1.60:161</t>
+          <t>192.168.1.60</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="F329" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.62:161</t>
+          <t>192.168.1.62</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.64:161</t>
+          <t>192.168.1.64</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>192.168.1.70:161</t>
+          <t>192.168.1.70</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.72:161</t>
+          <t>192.168.1.72</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.74:161</t>
+          <t>192.168.1.74</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>192.168.1.80:161</t>
+          <t>192.168.1.80</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.82:161</t>
+          <t>192.168.1.82</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.84:161</t>
+          <t>192.168.1.84</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="F348" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>192.168.1.30:161</t>
+          <t>192.168.1.30</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.32:161</t>
+          <t>192.168.1.32</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>192.168.1.34:161</t>
+          <t>192.168.1.34</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>192.168.1.40:161</t>
+          <t>192.168.1.40</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.42:161</t>
+          <t>192.168.1.42</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>192.168.1.44:161</t>
+          <t>192.168.1.44</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>192.168.1.30:161</t>
+          <t>192.168.1.30</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>192.168.1.32:161</t>
+          <t>192.168.1.32</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.34:161</t>
+          <t>192.168.1.34</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>192.168.1.134:161</t>
+          <t>192.168.1.134</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>192.168.1.134:161</t>
+          <t>192.168.1.134</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>192.168.1.136:161</t>
+          <t>192.168.1.136</t>
         </is>
       </c>
     </row>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="F414" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>192.168.1.30:161</t>
+          <t>192.168.1.30</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.32:161</t>
+          <t>192.168.1.32</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.34:161</t>
+          <t>192.168.1.34</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>192.168.1.40:161</t>
+          <t>192.168.1.40</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.42:161</t>
+          <t>192.168.1.42</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="F420" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.44:161</t>
+          <t>192.168.1.44</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>192.168.1.50:161</t>
+          <t>192.168.1.50</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>192.168.1.52:161</t>
+          <t>192.168.1.52</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="F423" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.54:161</t>
+          <t>192.168.1.54</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14466,7 +14466,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14818,7 +14818,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="F450" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -14946,7 +14946,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>192.168.1.1:161</t>
+          <t>192.168.1.1</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>192.168.1.10:161</t>
+          <t>192.168.1.10</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>192.168.1.12:161</t>
+          <t>192.168.1.12</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="F458" s="4" t="inlineStr">
         <is>
-          <t>192.168.1.14:161</t>
+          <t>192.168.1.14</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>192.168.1.20:161</t>
+          <t>192.168.1.20</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>192.168.1.22:161</t>
+          <t>192.168.1.22</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>192.168.1.24:161</t>
+          <t>192.168.1.24</t>
         </is>
       </c>
     </row>
